--- a/Excel/ARCC_Earnings.xlsx
+++ b/Excel/ARCC_Earnings.xlsx
@@ -413,41 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Announced</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Period End</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPS Actual</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS Est</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Surprise %</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -461,22 +466,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>1Q26</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.47</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.48</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,22 +496,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>4Q25</t>
         </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5</v>
       </c>
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,22 +526,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>3Q25</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.503</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -536,22 +556,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>2Q25</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.506</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -561,22 +586,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>1Q25</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.53</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-5.7</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -586,22 +616,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>4Q24</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>0.55</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.58</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -611,22 +646,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>3Q24</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>0.58</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.6</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-3.3</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -636,22 +676,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>2Q24</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>0.61</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>0.58</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.03</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>5.2</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,22 +706,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>1Q24</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>0.59</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>0.6</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -686,22 +736,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>4Q23</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>0.63</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>0.59</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.04</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>6.8</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -711,22 +766,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>3Q23</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>0.59</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>0.58</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.01</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>1.7</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -736,22 +796,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>2Q23</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>0.58</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>0.57</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.01</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1.8</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -761,22 +826,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>1Q23</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>0.57</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>0.59</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-3.4</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -786,22 +856,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>4Q22</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>0.63</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0.57</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>0.06</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>10.5</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -815,22 +890,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>3Q22</t>
         </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.5</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,22 +920,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>2Q22</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>0.52</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>0.43</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.09</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>20.9</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -869,22 +954,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>1Q22</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>0.42</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0.47</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-10.6</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -898,22 +988,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>4Q21</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>0.52</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.02</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -923,22 +1018,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>3Q21</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>0.47</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>0.45</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.02</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>4.4</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -948,22 +1048,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>2Q21</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>0.53</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>0.43</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.1</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>23.3</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -977,22 +1082,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>1Q21</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>0.43</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>0.42</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.01</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>2.4</v>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1002,22 +1112,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>4Q20</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>0.54</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0.4</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>0.14</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>35</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1031,22 +1146,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>3Q20</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>0.39</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>0.38</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>0.01</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>2.6</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1056,22 +1176,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>2Q20</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>0.39</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>0.38</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>0.01</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>2.6</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1081,22 +1206,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>1Q20</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>0.41</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0.43</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-4.7</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1106,22 +1236,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>2019-12-31</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>4Q19</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>0.46</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0.45</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>0.01</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>2.2</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1131,22 +1266,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>3Q19</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>0.48</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0.46</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>0.02</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>4.3</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1156,22 +1296,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>2Q19</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>0.49</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.44</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.05</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>11.4</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1185,22 +1330,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>2019-03-31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>1Q19</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>0.48</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>0.42</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>0.06</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>14.3</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1214,22 +1364,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>2018-12-31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>4Q18</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>0.45</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>0.41</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.04</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1239,22 +1394,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>2018-09-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>3Q18</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>0.45</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>0.4</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.05</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>12.5</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1268,22 +1428,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>2018-06-30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>2Q18</t>
         </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.39</v>
       </c>
       <c r="D33" t="n">
         <v>0.39</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1293,22 +1458,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>1Q18</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>0.39</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>0.37</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>0.02</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>5.4</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1318,22 +1488,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>2017-12-31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>4Q17</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>0.38</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>0.37</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>0.01</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>2.7</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1343,22 +1518,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>3Q17</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>0.36</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>0.35</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.01</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>2.9</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1368,22 +1548,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2017-06-30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2Q17</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>0.34</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>0.36</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>-5.6</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1393,22 +1578,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2017-03-31</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>1Q17</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>0.32</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>0.38</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>-15.8</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -1422,22 +1612,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2016-12-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>4Q16</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>0.42</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>0.39</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.03</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>7.7</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1447,22 +1642,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2016-09-30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>3Q16</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>0.43</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>0.39</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>0.04</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>10.3</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1476,22 +1676,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2016-06-30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2Q16</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>0.39</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>0.38</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>0.01</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>2.6</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1501,22 +1706,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>1Q16</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>0.37</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>0.39</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>-5.1</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1526,22 +1736,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2015-12-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>4Q15</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>0.4</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>0.39</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>0.01</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>2.6</v>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1551,22 +1766,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2015-09-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>3Q15</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>0.42</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>0.38</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>0.04</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>10.5</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1580,22 +1800,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2015-06-30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2Q15</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>0.35</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>0.38</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>-7.9</v>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1605,22 +1830,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2015-03-31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>1Q15</t>
         </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.39</v>
       </c>
       <c r="D46" t="n">
         <v>0.39</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1630,22 +1860,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-12-31</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>4Q14</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>0.41</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>0.39</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>0.02</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>5.1</v>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1655,22 +1890,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>3Q14</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>0.4</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>0.38</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>0.02</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>5.3</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1680,22 +1920,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2014-06-30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2Q14</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>0.34</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>0.37</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>-8.1</v>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1705,22 +1950,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2014-03-31</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>1Q14</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>0.38</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>0.39</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1730,22 +1980,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>4Q13</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>0.39</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>0.41</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>-4.9</v>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1755,22 +2010,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2013-09-30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>3Q13</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>0.47</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>0.39</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>0.08</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>20.5</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1784,22 +2044,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2013-06-30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2Q13</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>0.35</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>0.39</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>-10.3</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -1813,22 +2078,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2013-03-31</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>1Q13</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>0.38</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>0.39</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1838,22 +2108,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2012-12-31</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>4Q12</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>0.38</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>0.41</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>-7.3</v>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1863,22 +2138,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2012-09-30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>3Q12</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>0.42</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>0.41</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>0.01</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>2.4</v>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1888,22 +2168,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>2012-06-30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>2Q12</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>0.4</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>0.39</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>0.01</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>2.6</v>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1913,22 +2198,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2012-03-31</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>1Q12</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>0.38</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>0.39</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1938,22 +2228,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2011-12-31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>4Q11</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>0.48</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>0.39</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>0.09</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>23.1</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1967,22 +2262,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2011-09-30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>3Q11</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>0.43</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>0.37</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>0.06</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>16.2</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1996,22 +2296,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2011-06-30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2Q11</t>
         </is>
-      </c>
-      <c r="C61" t="n">
-        <v>0.34</v>
       </c>
       <c r="D61" t="n">
         <v>0.34</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2021,22 +2326,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2011-03-31</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>1Q11</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>0.31</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>0.34</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2046,22 +2356,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2011-03-31</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>1Q11</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>0.41</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>0.35</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>0.06</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>17.1</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -2075,22 +2390,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2010-09-30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>3Q10</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>0.37</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>0.33</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>0.04</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>12.1</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -2104,22 +2424,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>2Q10</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>0.26</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>0.31</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>-16.1</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2133,22 +2458,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2010-03-31</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>1Q10</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>0.25</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
         <v>0.33</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>-0.08</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>-24.2</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2162,22 +2492,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2009-12-31</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>4Q09</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>0.35</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
         <v>0.33</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>0.02</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>6.1</v>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2187,22 +2522,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>2009-09-30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>3Q09</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>0.32</v>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
         <v>0.35</v>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>-8.6</v>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2212,22 +2552,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>2Q09</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>0.33</v>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
         <v>0.31</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>0.02</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>6.5</v>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2237,22 +2582,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>2009-03-31</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>1Q09</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>0.31</v>
       </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
         <v>0.32</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>-3.1</v>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2262,22 +2612,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>2009-03-31</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>1Q09</t>
         </is>
-      </c>
-      <c r="C71" t="n">
-        <v>0.33</v>
       </c>
       <c r="D71" t="n">
         <v>0.33</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2287,22 +2642,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>2008-09-30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>3Q08</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>0.34</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
         <v>0.35</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>-2.9</v>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2312,22 +2672,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>2008-06-30</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>2Q08</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>0.4</v>
       </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
         <v>0.34</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>0.06</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>17.6</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -2341,22 +2706,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>2008-03-31</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>1Q08</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>0.35</v>
       </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
         <v>0.37</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>-5.4</v>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2366,22 +2736,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>4Q07</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>0.37</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>0.38</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2391,22 +2766,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>2007-09-30</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>3Q07</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>0.34</v>
       </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
         <v>0.37</v>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>-8.1</v>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2416,22 +2796,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>2Q07</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>0.36</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>0.35</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>0.01</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>2.9</v>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2441,22 +2826,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>2007-03-31</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>1Q07</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>0.36</v>
       </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
         <v>0.39</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>-7.7</v>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2466,22 +2856,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>2007-03-31</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>1Q07</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>0.38</v>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>0.4</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>-5</v>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2491,22 +2886,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>2006-09-30</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>3Q06</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>0.37</v>
       </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
         <v>0.38</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2516,22 +2916,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>2006-06-30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>2Q06</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>0.43</v>
       </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
         <v>0.35</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>0.08</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>22.9</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -2545,22 +2950,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>2006-03-31</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>1Q06</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>0.31</v>
       </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
         <v>0.32</v>
       </c>
-      <c r="E82" t="n">
+      <c r="F82" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>-3.1</v>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2570,22 +2980,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>4Q05</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>0.33</v>
       </c>
-      <c r="D83" t="n">
+      <c r="E83" t="n">
         <v>0.3</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>0.03</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>10</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -2599,22 +3014,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>2005-09-30</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>3Q05</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>0.3</v>
       </c>
-      <c r="D84" t="n">
+      <c r="E84" t="n">
         <v>0.31</v>
       </c>
-      <c r="E84" t="n">
+      <c r="F84" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>-3.2</v>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2624,22 +3044,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>2005-06-30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>2Q05</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>0.25</v>
       </c>
-      <c r="D85" t="n">
+      <c r="E85" t="n">
         <v>0.26</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>-3.8</v>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2649,22 +3074,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>2005-03-31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>1Q05</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>0.29</v>
       </c>
-      <c r="D86" t="n">
+      <c r="E86" t="n">
         <v>0.32</v>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>-9.4</v>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
